--- a/SelecciónDatasetsProyecto/ISTAC/ISTAC_datasets.xlsx
+++ b/SelecciónDatasetsProyecto/ISTAC/ISTAC_datasets.xlsx
@@ -578,6 +578,9 @@
     <t xml:space="preserve">2012-03</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-08</t>
+  </si>
+  <si>
     <t xml:space="preserve">AFILIACIONES_AGRICULTURA</t>
   </si>
   <si>
@@ -854,7 +857,7 @@
     <t xml:space="preserve">2003-W40</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-W34</t>
+    <t xml:space="preserve">2026-W36</t>
   </si>
   <si>
     <t xml:space="preserve">HIDROCARBUROS_PRECIO_GASOLINA95</t>
@@ -1379,9 +1382,6 @@
     <t xml:space="preserve">2010-Q3</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05</t>
-  </si>
-  <si>
     <t xml:space="preserve">PRESUPUESTO_CAN_IMPORTE_EJECUTADO_DEFINITIVO_INGRESO</t>
   </si>
   <si>
@@ -1397,15 +1397,18 @@
     <t xml:space="preserve">TRIBUTO_IBI_CUOTA_LIQUIDA_RUSTICO</t>
   </si>
   <si>
+    <t xml:space="preserve">2006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRIBUTO_IBI_CUOTA_LIQUIDA_URBANO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRIBUTO_IBI_TIPO_GRAVAMEN_RUSTICO</t>
+  </si>
+  <si>
     <t xml:space="preserve">1990</t>
   </si>
   <si>
-    <t xml:space="preserve">TRIBUTO_IBI_CUOTA_LIQUIDA_URBANO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRIBUTO_IBI_TIPO_GRAVAMEN_RUSTICO</t>
-  </si>
-  <si>
     <t xml:space="preserve">TRIBUTO_IBI_TIPO_GRAVAMEN_URBANO</t>
   </si>
   <si>
@@ -1494,9 +1497,6 @@
   </si>
   <si>
     <t xml:space="preserve">Servicios financieros, monetarios y seguros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2006</t>
   </si>
   <si>
     <t xml:space="preserve">HIPOTECAS_CONSTITUIDAS</t>
@@ -5042,7 +5042,7 @@
         <v>97</v>
       </c>
       <c r="E104" t="n">
-        <v>52380</v>
+        <v>52865</v>
       </c>
       <c r="F104" t="s">
         <v>11</v>
@@ -5054,7 +5054,7 @@
         <v>187</v>
       </c>
       <c r="I104" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="105">
@@ -5062,7 +5062,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C105" t="s">
         <v>183</v>
@@ -5071,7 +5071,7 @@
         <v>97</v>
       </c>
       <c r="E105" t="n">
-        <v>3395</v>
+        <v>3880</v>
       </c>
       <c r="F105" t="s">
         <v>11</v>
@@ -5080,10 +5080,10 @@
         <v>27</v>
       </c>
       <c r="H105" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I105" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="106">
@@ -5091,7 +5091,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C106" t="s">
         <v>183</v>
@@ -5100,7 +5100,7 @@
         <v>9</v>
       </c>
       <c r="E106" t="n">
-        <v>315</v>
+        <v>360</v>
       </c>
       <c r="F106" t="s">
         <v>26</v>
@@ -5109,10 +5109,10 @@
         <v>27</v>
       </c>
       <c r="H106" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I106" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="107">
@@ -5120,7 +5120,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C107" t="s">
         <v>183</v>
@@ -5129,7 +5129,7 @@
         <v>97</v>
       </c>
       <c r="E107" t="n">
-        <v>52380</v>
+        <v>52865</v>
       </c>
       <c r="F107" t="s">
         <v>11</v>
@@ -5141,7 +5141,7 @@
         <v>187</v>
       </c>
       <c r="I107" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="108">
@@ -5149,7 +5149,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C108" t="s">
         <v>183</v>
@@ -5158,7 +5158,7 @@
         <v>97</v>
       </c>
       <c r="E108" t="n">
-        <v>52380</v>
+        <v>52865</v>
       </c>
       <c r="F108" t="s">
         <v>11</v>
@@ -5170,7 +5170,7 @@
         <v>187</v>
       </c>
       <c r="I108" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="109">
@@ -5178,7 +5178,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C109" t="s">
         <v>183</v>
@@ -5187,7 +5187,7 @@
         <v>97</v>
       </c>
       <c r="E109" t="n">
-        <v>52380</v>
+        <v>52865</v>
       </c>
       <c r="F109" t="s">
         <v>11</v>
@@ -5199,7 +5199,7 @@
         <v>187</v>
       </c>
       <c r="I109" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="110">
@@ -5207,7 +5207,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C110" t="s">
         <v>183</v>
@@ -5216,7 +5216,7 @@
         <v>97</v>
       </c>
       <c r="E110" t="n">
-        <v>52380</v>
+        <v>52865</v>
       </c>
       <c r="F110" t="s">
         <v>11</v>
@@ -5228,7 +5228,7 @@
         <v>187</v>
       </c>
       <c r="I110" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="111">
@@ -5236,7 +5236,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C111" t="s">
         <v>183</v>
@@ -5245,7 +5245,7 @@
         <v>97</v>
       </c>
       <c r="E111" t="n">
-        <v>52380</v>
+        <v>52865</v>
       </c>
       <c r="F111" t="s">
         <v>11</v>
@@ -5257,7 +5257,7 @@
         <v>187</v>
       </c>
       <c r="I111" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="112">
@@ -5265,7 +5265,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C112" t="s">
         <v>183</v>
@@ -5274,7 +5274,7 @@
         <v>97</v>
       </c>
       <c r="E112" t="n">
-        <v>52380</v>
+        <v>52865</v>
       </c>
       <c r="F112" t="s">
         <v>11</v>
@@ -5286,7 +5286,7 @@
         <v>187</v>
       </c>
       <c r="I112" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="113">
@@ -5294,7 +5294,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C113" t="s">
         <v>183</v>
@@ -5303,7 +5303,7 @@
         <v>97</v>
       </c>
       <c r="E113" t="n">
-        <v>3395</v>
+        <v>3880</v>
       </c>
       <c r="F113" t="s">
         <v>11</v>
@@ -5312,10 +5312,10 @@
         <v>27</v>
       </c>
       <c r="H113" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I113" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="114">
@@ -5323,7 +5323,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C114" t="s">
         <v>183</v>
@@ -5332,7 +5332,7 @@
         <v>97</v>
       </c>
       <c r="E114" t="n">
-        <v>52380</v>
+        <v>52865</v>
       </c>
       <c r="F114" t="s">
         <v>11</v>
@@ -5344,7 +5344,7 @@
         <v>187</v>
       </c>
       <c r="I114" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="115">
@@ -5352,7 +5352,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C115" t="s">
         <v>183</v>
@@ -5361,7 +5361,7 @@
         <v>97</v>
       </c>
       <c r="E115" t="n">
-        <v>3395</v>
+        <v>3880</v>
       </c>
       <c r="F115" t="s">
         <v>11</v>
@@ -5370,10 +5370,10 @@
         <v>27</v>
       </c>
       <c r="H115" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I115" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="116">
@@ -5381,7 +5381,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C116" t="s">
         <v>183</v>
@@ -5390,7 +5390,7 @@
         <v>97</v>
       </c>
       <c r="E116" t="n">
-        <v>52380</v>
+        <v>52865</v>
       </c>
       <c r="F116" t="s">
         <v>11</v>
@@ -5402,7 +5402,7 @@
         <v>187</v>
       </c>
       <c r="I116" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="117">
@@ -5410,7 +5410,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C117" t="s">
         <v>183</v>
@@ -5419,7 +5419,7 @@
         <v>96</v>
       </c>
       <c r="E117" t="n">
-        <v>51840</v>
+        <v>52320</v>
       </c>
       <c r="F117" t="s">
         <v>11</v>
@@ -5431,7 +5431,7 @@
         <v>187</v>
       </c>
       <c r="I117" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="118">
@@ -5439,7 +5439,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C118" t="s">
         <v>183</v>
@@ -5448,7 +5448,7 @@
         <v>96</v>
       </c>
       <c r="E118" t="n">
-        <v>51840</v>
+        <v>52320</v>
       </c>
       <c r="F118" t="s">
         <v>11</v>
@@ -5460,7 +5460,7 @@
         <v>187</v>
       </c>
       <c r="I118" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="119">
@@ -5468,7 +5468,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C119" t="s">
         <v>183</v>
@@ -5477,7 +5477,7 @@
         <v>96</v>
       </c>
       <c r="E119" t="n">
-        <v>51840</v>
+        <v>52320</v>
       </c>
       <c r="F119" t="s">
         <v>11</v>
@@ -5489,7 +5489,7 @@
         <v>187</v>
       </c>
       <c r="I119" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="120">
@@ -5497,7 +5497,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C120" t="s">
         <v>183</v>
@@ -5506,7 +5506,7 @@
         <v>9</v>
       </c>
       <c r="E120" t="n">
-        <v>315</v>
+        <v>360</v>
       </c>
       <c r="F120" t="s">
         <v>26</v>
@@ -5515,10 +5515,10 @@
         <v>27</v>
       </c>
       <c r="H120" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I120" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="121">
@@ -5526,7 +5526,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C121" t="s">
         <v>183</v>
@@ -5535,7 +5535,7 @@
         <v>8</v>
       </c>
       <c r="E121" t="n">
-        <v>3000</v>
+        <v>3040</v>
       </c>
       <c r="F121" t="s">
         <v>26</v>
@@ -5544,10 +5544,10 @@
         <v>27</v>
       </c>
       <c r="H121" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I121" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="122">
@@ -5555,7 +5555,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C122" t="s">
         <v>183</v>
@@ -5564,7 +5564,7 @@
         <v>97</v>
       </c>
       <c r="E122" t="n">
-        <v>3395</v>
+        <v>3880</v>
       </c>
       <c r="F122" t="s">
         <v>11</v>
@@ -5573,10 +5573,10 @@
         <v>27</v>
       </c>
       <c r="H122" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I122" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="123">
@@ -5584,7 +5584,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C123" t="s">
         <v>183</v>
@@ -5593,7 +5593,7 @@
         <v>9</v>
       </c>
       <c r="E123" t="n">
-        <v>315</v>
+        <v>360</v>
       </c>
       <c r="F123" t="s">
         <v>26</v>
@@ -5602,10 +5602,10 @@
         <v>27</v>
       </c>
       <c r="H123" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I123" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="124">
@@ -5613,7 +5613,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C124" t="s">
         <v>183</v>
@@ -5642,7 +5642,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C125" t="s">
         <v>183</v>
@@ -5671,7 +5671,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C126" t="s">
         <v>183</v>
@@ -5700,7 +5700,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C127" t="s">
         <v>183</v>
@@ -5729,7 +5729,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C128" t="s">
         <v>183</v>
@@ -5758,7 +5758,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C129" t="s">
         <v>183</v>
@@ -5787,7 +5787,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C130" t="s">
         <v>183</v>
@@ -5816,7 +5816,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C131" t="s">
         <v>183</v>
@@ -5845,7 +5845,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C132" t="s">
         <v>183</v>
@@ -5874,7 +5874,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C133" t="s">
         <v>183</v>
@@ -5903,7 +5903,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C134" t="s">
         <v>183</v>
@@ -5932,7 +5932,7 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C135" t="s">
         <v>183</v>
@@ -5941,7 +5941,7 @@
         <v>96</v>
       </c>
       <c r="E135" t="n">
-        <v>106080</v>
+        <v>106560</v>
       </c>
       <c r="F135" t="s">
         <v>11</v>
@@ -5950,10 +5950,10 @@
         <v>27</v>
       </c>
       <c r="H135" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I135" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="136">
@@ -5961,7 +5961,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C136" t="s">
         <v>183</v>
@@ -5970,7 +5970,7 @@
         <v>96</v>
       </c>
       <c r="E136" t="n">
-        <v>106080</v>
+        <v>106560</v>
       </c>
       <c r="F136" t="s">
         <v>11</v>
@@ -5979,10 +5979,10 @@
         <v>27</v>
       </c>
       <c r="H136" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I136" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="137">
@@ -5990,7 +5990,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C137" t="s">
         <v>183</v>
@@ -5999,7 +5999,7 @@
         <v>96</v>
       </c>
       <c r="E137" t="n">
-        <v>106080</v>
+        <v>106560</v>
       </c>
       <c r="F137" t="s">
         <v>11</v>
@@ -6008,10 +6008,10 @@
         <v>27</v>
       </c>
       <c r="H137" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I137" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="138">
@@ -6019,7 +6019,7 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C138" t="s">
         <v>183</v>
@@ -6037,7 +6037,7 @@
         <v>43</v>
       </c>
       <c r="H138" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I138" t="s">
         <v>118</v>
@@ -6048,7 +6048,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C139" t="s">
         <v>183</v>
@@ -6066,7 +6066,7 @@
         <v>43</v>
       </c>
       <c r="H139" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I139" t="s">
         <v>118</v>
@@ -6077,7 +6077,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C140" t="s">
         <v>183</v>
@@ -6095,7 +6095,7 @@
         <v>43</v>
       </c>
       <c r="H140" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I140" t="s">
         <v>118</v>
@@ -6106,7 +6106,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C141" t="s">
         <v>183</v>
@@ -6124,7 +6124,7 @@
         <v>43</v>
       </c>
       <c r="H141" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I141" t="s">
         <v>118</v>
@@ -6135,7 +6135,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C142" t="s">
         <v>183</v>
@@ -6153,7 +6153,7 @@
         <v>43</v>
       </c>
       <c r="H142" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I142" t="s">
         <v>118</v>
@@ -6164,7 +6164,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C143" t="s">
         <v>183</v>
@@ -6182,7 +6182,7 @@
         <v>43</v>
       </c>
       <c r="H143" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I143" t="s">
         <v>118</v>
@@ -6193,7 +6193,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C144" t="s">
         <v>183</v>
@@ -6211,7 +6211,7 @@
         <v>43</v>
       </c>
       <c r="H144" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I144" t="s">
         <v>118</v>
@@ -6222,7 +6222,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C145" t="s">
         <v>183</v>
@@ -6240,7 +6240,7 @@
         <v>43</v>
       </c>
       <c r="H145" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I145" t="s">
         <v>118</v>
@@ -6251,7 +6251,7 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C146" t="s">
         <v>183</v>
@@ -6269,7 +6269,7 @@
         <v>43</v>
       </c>
       <c r="H146" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I146" t="s">
         <v>118</v>
@@ -6280,7 +6280,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C147" t="s">
         <v>183</v>
@@ -6298,7 +6298,7 @@
         <v>43</v>
       </c>
       <c r="H147" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I147" t="s">
         <v>118</v>
@@ -6309,7 +6309,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C148" t="s">
         <v>183</v>
@@ -6327,7 +6327,7 @@
         <v>43</v>
       </c>
       <c r="H148" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I148" t="s">
         <v>118</v>
@@ -6338,7 +6338,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C149" t="s">
         <v>183</v>
@@ -6356,7 +6356,7 @@
         <v>43</v>
       </c>
       <c r="H149" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I149" t="s">
         <v>118</v>
@@ -6367,7 +6367,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C150" t="s">
         <v>183</v>
@@ -6385,7 +6385,7 @@
         <v>43</v>
       </c>
       <c r="H150" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I150" t="s">
         <v>118</v>
@@ -6396,7 +6396,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C151" t="s">
         <v>183</v>
@@ -6414,7 +6414,7 @@
         <v>43</v>
       </c>
       <c r="H151" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I151" t="s">
         <v>118</v>
@@ -6425,7 +6425,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C152" t="s">
         <v>183</v>
@@ -6443,7 +6443,7 @@
         <v>43</v>
       </c>
       <c r="H152" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I152" t="s">
         <v>118</v>
@@ -6454,7 +6454,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C153" t="s">
         <v>183</v>
@@ -6472,7 +6472,7 @@
         <v>43</v>
       </c>
       <c r="H153" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I153" t="s">
         <v>118</v>
@@ -6483,7 +6483,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C154" t="s">
         <v>183</v>
@@ -6501,7 +6501,7 @@
         <v>43</v>
       </c>
       <c r="H154" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I154" t="s">
         <v>118</v>
@@ -6512,7 +6512,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C155" t="s">
         <v>183</v>
@@ -6530,7 +6530,7 @@
         <v>43</v>
       </c>
       <c r="H155" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I155" t="s">
         <v>118</v>
@@ -6541,7 +6541,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C156" t="s">
         <v>183</v>
@@ -6559,7 +6559,7 @@
         <v>43</v>
       </c>
       <c r="H156" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I156" t="s">
         <v>118</v>
@@ -6570,7 +6570,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C157" t="s">
         <v>183</v>
@@ -6588,7 +6588,7 @@
         <v>43</v>
       </c>
       <c r="H157" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I157" t="s">
         <v>118</v>
@@ -6599,7 +6599,7 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C158" t="s">
         <v>183</v>
@@ -6617,7 +6617,7 @@
         <v>43</v>
       </c>
       <c r="H158" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I158" t="s">
         <v>118</v>
@@ -6628,16 +6628,16 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C159" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D159" t="n">
         <v>3</v>
       </c>
       <c r="E159" t="n">
-        <v>2625</v>
+        <v>2640</v>
       </c>
       <c r="F159" t="s">
         <v>156</v>
@@ -6646,10 +6646,10 @@
         <v>27</v>
       </c>
       <c r="H159" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I159" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="160">
@@ -6657,16 +6657,16 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C160" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D160" t="n">
         <v>3</v>
       </c>
       <c r="E160" t="n">
-        <v>2625</v>
+        <v>2640</v>
       </c>
       <c r="F160" t="s">
         <v>156</v>
@@ -6675,10 +6675,10 @@
         <v>27</v>
       </c>
       <c r="H160" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I160" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="161">
@@ -6686,16 +6686,16 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C161" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D161" t="n">
         <v>3</v>
       </c>
       <c r="E161" t="n">
-        <v>2625</v>
+        <v>2640</v>
       </c>
       <c r="F161" t="s">
         <v>156</v>
@@ -6704,10 +6704,10 @@
         <v>27</v>
       </c>
       <c r="H161" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I161" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="162">
@@ -6715,10 +6715,10 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C162" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D162" t="n">
         <v>96</v>
@@ -6733,7 +6733,7 @@
         <v>43</v>
       </c>
       <c r="H162" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I162" t="s">
         <v>118</v>
@@ -6744,10 +6744,10 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C163" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D163" t="n">
         <v>96</v>
@@ -6762,7 +6762,7 @@
         <v>43</v>
       </c>
       <c r="H163" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I163" t="s">
         <v>118</v>
@@ -6773,10 +6773,10 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C164" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D164" t="n">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>27</v>
       </c>
       <c r="H164" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I164" t="s">
         <v>86</v>
@@ -6802,10 +6802,10 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C165" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D165" t="n">
         <v>8</v>
@@ -6820,7 +6820,7 @@
         <v>27</v>
       </c>
       <c r="H165" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I165" t="s">
         <v>86</v>
@@ -6831,10 +6831,10 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C166" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D166" t="n">
         <v>20</v>
@@ -6860,16 +6860,16 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
+        <v>261</v>
+      </c>
+      <c r="C167" t="s">
         <v>260</v>
-      </c>
-      <c r="C167" t="s">
-        <v>259</v>
       </c>
       <c r="D167" t="n">
         <v>97</v>
       </c>
       <c r="E167" t="n">
-        <v>59170</v>
+        <v>59655</v>
       </c>
       <c r="F167" t="s">
         <v>11</v>
@@ -6881,7 +6881,7 @@
         <v>37</v>
       </c>
       <c r="I167" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="168">
@@ -6889,16 +6889,16 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C168" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D168" t="n">
         <v>96</v>
       </c>
       <c r="E168" t="n">
-        <v>3360</v>
+        <v>3840</v>
       </c>
       <c r="F168" t="s">
         <v>11</v>
@@ -6907,10 +6907,10 @@
         <v>27</v>
       </c>
       <c r="H168" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I168" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="169">
@@ -6918,16 +6918,16 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C169" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D169" t="n">
         <v>9</v>
       </c>
       <c r="E169" t="n">
-        <v>315</v>
+        <v>360</v>
       </c>
       <c r="F169" t="s">
         <v>26</v>
@@ -6936,10 +6936,10 @@
         <v>27</v>
       </c>
       <c r="H169" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I169" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="170">
@@ -6947,16 +6947,16 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C170" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D170" t="n">
         <v>96</v>
       </c>
       <c r="E170" t="n">
-        <v>3360</v>
+        <v>3840</v>
       </c>
       <c r="F170" t="s">
         <v>11</v>
@@ -6965,10 +6965,10 @@
         <v>27</v>
       </c>
       <c r="H170" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I170" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="171">
@@ -6976,16 +6976,16 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C171" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D171" t="n">
         <v>96</v>
       </c>
       <c r="E171" t="n">
-        <v>3360</v>
+        <v>3840</v>
       </c>
       <c r="F171" t="s">
         <v>11</v>
@@ -6994,10 +6994,10 @@
         <v>27</v>
       </c>
       <c r="H171" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I171" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="172">
@@ -7005,16 +7005,16 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C172" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D172" t="n">
         <v>9</v>
       </c>
       <c r="E172" t="n">
-        <v>315</v>
+        <v>360</v>
       </c>
       <c r="F172" t="s">
         <v>26</v>
@@ -7023,10 +7023,10 @@
         <v>27</v>
       </c>
       <c r="H172" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I172" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="173">
@@ -7034,16 +7034,16 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D173" t="n">
         <v>96</v>
       </c>
       <c r="E173" t="n">
-        <v>3360</v>
+        <v>3840</v>
       </c>
       <c r="F173" t="s">
         <v>11</v>
@@ -7052,10 +7052,10 @@
         <v>27</v>
       </c>
       <c r="H173" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I173" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="174">
@@ -7063,16 +7063,16 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D174" t="n">
         <v>8</v>
       </c>
       <c r="E174" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="F174" t="s">
         <v>26</v>
@@ -7081,10 +7081,10 @@
         <v>27</v>
       </c>
       <c r="H174" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I174" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
     </row>
     <row r="175">
@@ -7092,10 +7092,10 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D175" t="n">
         <v>8</v>
@@ -7110,7 +7110,7 @@
         <v>27</v>
       </c>
       <c r="H175" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I175" t="s">
         <v>86</v>
@@ -7121,16 +7121,16 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D176" t="n">
         <v>63</v>
       </c>
       <c r="E176" t="n">
-        <v>128835</v>
+        <v>129150</v>
       </c>
       <c r="F176" t="s">
         <v>20</v>
@@ -7139,10 +7139,10 @@
         <v>27</v>
       </c>
       <c r="H176" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I176" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
     </row>
     <row r="177">
@@ -7150,16 +7150,16 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C177" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D177" t="n">
         <v>63</v>
       </c>
       <c r="E177" t="n">
-        <v>128835</v>
+        <v>129150</v>
       </c>
       <c r="F177" t="s">
         <v>20</v>
@@ -7168,10 +7168,10 @@
         <v>27</v>
       </c>
       <c r="H177" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I177" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
     </row>
     <row r="178">
@@ -7179,16 +7179,16 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C178" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D178" t="n">
         <v>63</v>
       </c>
       <c r="E178" t="n">
-        <v>128835</v>
+        <v>129150</v>
       </c>
       <c r="F178" t="s">
         <v>20</v>
@@ -7197,10 +7197,10 @@
         <v>27</v>
       </c>
       <c r="H178" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I178" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
     </row>
     <row r="179">
@@ -7208,16 +7208,16 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C179" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D179" t="n">
         <v>63</v>
       </c>
       <c r="E179" t="n">
-        <v>128835</v>
+        <v>129150</v>
       </c>
       <c r="F179" t="s">
         <v>20</v>
@@ -7226,10 +7226,10 @@
         <v>27</v>
       </c>
       <c r="H179" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I179" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
     </row>
     <row r="180">
@@ -7237,10 +7237,10 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C180" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D180" t="n">
         <v>8</v>
@@ -7255,7 +7255,7 @@
         <v>27</v>
       </c>
       <c r="H180" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I180" t="s">
         <v>29</v>
@@ -7266,28 +7266,28 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C181" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D181" t="n">
         <v>8</v>
       </c>
       <c r="E181" t="n">
-        <v>47800</v>
+        <v>47880</v>
       </c>
       <c r="F181" t="s">
         <v>26</v>
       </c>
       <c r="G181" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H181" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I181" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="182">
@@ -7295,28 +7295,28 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C182" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D182" t="n">
         <v>8</v>
       </c>
       <c r="E182" t="n">
-        <v>47800</v>
+        <v>47880</v>
       </c>
       <c r="F182" t="s">
         <v>26</v>
       </c>
       <c r="G182" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H182" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I182" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="183">
@@ -7324,28 +7324,28 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C183" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D183" t="n">
         <v>8</v>
       </c>
       <c r="E183" t="n">
-        <v>47800</v>
+        <v>47880</v>
       </c>
       <c r="F183" t="s">
         <v>26</v>
       </c>
       <c r="G183" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H183" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I183" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="184">
@@ -7353,10 +7353,10 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C184" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D184" t="n">
         <v>3</v>
@@ -7382,10 +7382,10 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
+        <v>286</v>
+      </c>
+      <c r="C185" t="s">
         <v>285</v>
-      </c>
-      <c r="C185" t="s">
-        <v>284</v>
       </c>
       <c r="D185" t="n">
         <v>3</v>
@@ -7411,10 +7411,10 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C186" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D186" t="n">
         <v>3</v>
@@ -7440,10 +7440,10 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C187" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D187" t="n">
         <v>1</v>
@@ -7458,7 +7458,7 @@
         <v>12</v>
       </c>
       <c r="H187" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I187" t="s">
         <v>14</v>
@@ -7469,10 +7469,10 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C188" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D188" t="n">
         <v>1</v>
@@ -7487,7 +7487,7 @@
         <v>12</v>
       </c>
       <c r="H188" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I188" t="s">
         <v>14</v>
@@ -7498,10 +7498,10 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C189" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D189" t="n">
         <v>7</v>
@@ -7516,10 +7516,10 @@
         <v>27</v>
       </c>
       <c r="H189" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I189" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="190">
@@ -7527,10 +7527,10 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C190" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D190" t="n">
         <v>1</v>
@@ -7556,10 +7556,10 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
+        <v>297</v>
+      </c>
+      <c r="C191" t="s">
         <v>296</v>
-      </c>
-      <c r="C191" t="s">
-        <v>295</v>
       </c>
       <c r="D191" t="n">
         <v>1</v>
@@ -7585,10 +7585,10 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C192" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D192" t="n">
         <v>1</v>
@@ -7614,10 +7614,10 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C193" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D193" t="n">
         <v>1</v>
@@ -7643,10 +7643,10 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C194" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D194" t="n">
         <v>97</v>
@@ -7672,10 +7672,10 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
+        <v>302</v>
+      </c>
+      <c r="C195" t="s">
         <v>301</v>
-      </c>
-      <c r="C195" t="s">
-        <v>300</v>
       </c>
       <c r="D195" t="n">
         <v>97</v>
@@ -7701,10 +7701,10 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C196" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D196" t="n">
         <v>97</v>
@@ -7730,10 +7730,10 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C197" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D197" t="n">
         <v>97</v>
@@ -7759,10 +7759,10 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C198" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D198" t="n">
         <v>44</v>
@@ -7788,10 +7788,10 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
+        <v>307</v>
+      </c>
+      <c r="C199" t="s">
         <v>306</v>
-      </c>
-      <c r="C199" t="s">
-        <v>305</v>
       </c>
       <c r="D199" t="n">
         <v>44</v>
@@ -7817,10 +7817,10 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C200" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D200" t="n">
         <v>44</v>
@@ -7846,10 +7846,10 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C201" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D201" t="n">
         <v>44</v>
@@ -7875,10 +7875,10 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C202" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D202" t="n">
         <v>44</v>
@@ -7904,10 +7904,10 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C203" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D203" t="n">
         <v>44</v>
@@ -7933,10 +7933,10 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C204" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D204" t="n">
         <v>8</v>
@@ -7951,7 +7951,7 @@
         <v>27</v>
       </c>
       <c r="H204" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I204" t="s">
         <v>86</v>
@@ -7962,10 +7962,10 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C205" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D205" t="n">
         <v>8</v>
@@ -7980,7 +7980,7 @@
         <v>27</v>
       </c>
       <c r="H205" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I205" t="s">
         <v>86</v>
@@ -7991,10 +7991,10 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C206" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D206" t="n">
         <v>44</v>
@@ -8020,10 +8020,10 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C207" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D207" t="n">
         <v>44</v>
@@ -8049,10 +8049,10 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C208" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D208" t="n">
         <v>44</v>
@@ -8078,10 +8078,10 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C209" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D209" t="n">
         <v>44</v>
@@ -8107,10 +8107,10 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C210" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D210" t="n">
         <v>44</v>
@@ -8136,10 +8136,10 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C211" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D211" t="n">
         <v>44</v>
@@ -8165,10 +8165,10 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C212" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D212" t="n">
         <v>44</v>
@@ -8194,10 +8194,10 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C213" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D213" t="n">
         <v>44</v>
@@ -8223,10 +8223,10 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C214" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D214" t="n">
         <v>1</v>
@@ -8241,7 +8241,7 @@
         <v>43</v>
       </c>
       <c r="H214" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I214" t="s">
         <v>118</v>
@@ -8252,10 +8252,10 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C215" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D215" t="n">
         <v>6</v>
@@ -8270,7 +8270,7 @@
         <v>43</v>
       </c>
       <c r="H215" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I215" t="s">
         <v>118</v>
@@ -8281,10 +8281,10 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C216" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D216" t="n">
         <v>6</v>
@@ -8299,7 +8299,7 @@
         <v>43</v>
       </c>
       <c r="H216" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I216" t="s">
         <v>118</v>
@@ -8310,16 +8310,16 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C217" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D217" t="n">
         <v>6</v>
       </c>
       <c r="E217" t="n">
-        <v>6390</v>
+        <v>6420</v>
       </c>
       <c r="F217" t="s">
         <v>26</v>
@@ -8328,10 +8328,10 @@
         <v>27</v>
       </c>
       <c r="H217" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I217" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
     </row>
     <row r="218">
@@ -8339,16 +8339,16 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C218" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D218" t="n">
         <v>6</v>
       </c>
       <c r="E218" t="n">
-        <v>6390</v>
+        <v>6420</v>
       </c>
       <c r="F218" t="s">
         <v>26</v>
@@ -8357,10 +8357,10 @@
         <v>27</v>
       </c>
       <c r="H218" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I218" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
     </row>
     <row r="219">
@@ -8368,16 +8368,16 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C219" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D219" t="n">
         <v>6</v>
       </c>
       <c r="E219" t="n">
-        <v>6390</v>
+        <v>6420</v>
       </c>
       <c r="F219" t="s">
         <v>26</v>
@@ -8386,10 +8386,10 @@
         <v>27</v>
       </c>
       <c r="H219" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I219" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
     </row>
     <row r="220">
@@ -8397,10 +8397,10 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C220" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D220" t="n">
         <v>1</v>
@@ -8415,7 +8415,7 @@
         <v>12</v>
       </c>
       <c r="H220" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I220" t="s">
         <v>60</v>
@@ -8426,10 +8426,10 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C221" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D221" t="n">
         <v>1</v>
@@ -8444,7 +8444,7 @@
         <v>12</v>
       </c>
       <c r="H221" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I221" t="s">
         <v>60</v>
@@ -8455,10 +8455,10 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C222" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D222" t="n">
         <v>1</v>
@@ -8473,7 +8473,7 @@
         <v>12</v>
       </c>
       <c r="H222" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I222" t="s">
         <v>60</v>
@@ -8484,10 +8484,10 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C223" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D223" t="n">
         <v>1</v>
@@ -8502,7 +8502,7 @@
         <v>12</v>
       </c>
       <c r="H223" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I223" t="s">
         <v>60</v>
@@ -8513,10 +8513,10 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C224" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D224" t="n">
         <v>4</v>
@@ -8531,7 +8531,7 @@
         <v>43</v>
       </c>
       <c r="H224" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I224" t="s">
         <v>45</v>
@@ -8542,10 +8542,10 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C225" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D225" t="n">
         <v>4</v>
@@ -8560,7 +8560,7 @@
         <v>27</v>
       </c>
       <c r="H225" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I225" t="s">
         <v>29</v>
@@ -8571,10 +8571,10 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C226" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D226" t="n">
         <v>8</v>
@@ -8600,10 +8600,10 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C227" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D227" t="n">
         <v>4</v>
@@ -8618,7 +8618,7 @@
         <v>43</v>
       </c>
       <c r="H227" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I227" t="s">
         <v>45</v>
@@ -8629,10 +8629,10 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C228" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D228" t="n">
         <v>3</v>
@@ -8647,7 +8647,7 @@
         <v>27</v>
       </c>
       <c r="H228" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I228" t="s">
         <v>86</v>
@@ -8658,10 +8658,10 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C229" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D229" t="n">
         <v>3</v>
@@ -8676,7 +8676,7 @@
         <v>27</v>
       </c>
       <c r="H229" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I229" t="s">
         <v>86</v>
@@ -8687,10 +8687,10 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C230" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D230" t="n">
         <v>3</v>
@@ -8705,7 +8705,7 @@
         <v>27</v>
       </c>
       <c r="H230" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="I230" t="s">
         <v>86</v>
@@ -8716,10 +8716,10 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C231" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D231" t="n">
         <v>20</v>
@@ -8745,10 +8745,10 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
+        <v>347</v>
+      </c>
+      <c r="C232" t="s">
         <v>346</v>
-      </c>
-      <c r="C232" t="s">
-        <v>345</v>
       </c>
       <c r="D232" t="n">
         <v>1</v>
@@ -8774,10 +8774,10 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C233" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D233" t="n">
         <v>1</v>
@@ -8803,10 +8803,10 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C234" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D234" t="n">
         <v>2</v>
@@ -8821,7 +8821,7 @@
         <v>27</v>
       </c>
       <c r="H234" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I234" t="s">
         <v>29</v>
@@ -8832,10 +8832,10 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C235" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D235" t="n">
         <v>2</v>
@@ -8850,7 +8850,7 @@
         <v>27</v>
       </c>
       <c r="H235" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I235" t="s">
         <v>29</v>
@@ -8861,10 +8861,10 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C236" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D236" t="n">
         <v>2</v>
@@ -8879,7 +8879,7 @@
         <v>27</v>
       </c>
       <c r="H236" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I236" t="s">
         <v>29</v>
@@ -8890,16 +8890,16 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C237" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D237" t="n">
         <v>18</v>
       </c>
       <c r="E237" t="n">
-        <v>13932</v>
+        <v>13986</v>
       </c>
       <c r="F237" t="s">
         <v>20</v>
@@ -8911,7 +8911,7 @@
         <v>89</v>
       </c>
       <c r="I237" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
     </row>
     <row r="238">
@@ -8919,16 +8919,16 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C238" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D238" t="n">
         <v>2</v>
       </c>
       <c r="E238" t="n">
-        <v>1548</v>
+        <v>1554</v>
       </c>
       <c r="F238" t="s">
         <v>88</v>
@@ -8940,7 +8940,7 @@
         <v>89</v>
       </c>
       <c r="I238" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
     </row>
     <row r="239">
@@ -8948,16 +8948,16 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C239" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D239" t="n">
         <v>2</v>
       </c>
       <c r="E239" t="n">
-        <v>1548</v>
+        <v>1554</v>
       </c>
       <c r="F239" t="s">
         <v>88</v>
@@ -8969,7 +8969,7 @@
         <v>89</v>
       </c>
       <c r="I239" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
     </row>
     <row r="240">
@@ -8977,10 +8977,10 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C240" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D240" t="n">
         <v>18</v>
@@ -9006,10 +9006,10 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C241" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D241" t="n">
         <v>2</v>
@@ -9035,10 +9035,10 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
+        <v>358</v>
+      </c>
+      <c r="C242" t="s">
         <v>357</v>
-      </c>
-      <c r="C242" t="s">
-        <v>356</v>
       </c>
       <c r="D242" t="n">
         <v>2</v>
@@ -9064,10 +9064,10 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C243" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D243" t="n">
         <v>3</v>
@@ -9085,7 +9085,7 @@
         <v>146</v>
       </c>
       <c r="I243" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="244">
@@ -9093,10 +9093,10 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C244" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D244" t="n">
         <v>3</v>
@@ -9114,7 +9114,7 @@
         <v>146</v>
       </c>
       <c r="I244" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="245">
@@ -9122,10 +9122,10 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C245" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D245" t="n">
         <v>3</v>
@@ -9143,7 +9143,7 @@
         <v>146</v>
       </c>
       <c r="I245" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="246">
@@ -9151,10 +9151,10 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C246" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D246" t="n">
         <v>1</v>
@@ -9169,7 +9169,7 @@
         <v>12</v>
       </c>
       <c r="H246" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I246" t="s">
         <v>60</v>
@@ -9180,10 +9180,10 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C247" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D247" t="n">
         <v>1</v>
@@ -9198,7 +9198,7 @@
         <v>27</v>
       </c>
       <c r="H247" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I247" t="s">
         <v>29</v>
@@ -9209,10 +9209,10 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C248" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D248" t="n">
         <v>1</v>
@@ -9227,7 +9227,7 @@
         <v>27</v>
       </c>
       <c r="H248" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I248" t="s">
         <v>29</v>
@@ -9238,10 +9238,10 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C249" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D249" t="n">
         <v>1</v>
@@ -9256,7 +9256,7 @@
         <v>27</v>
       </c>
       <c r="H249" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I249" t="s">
         <v>29</v>
@@ -9267,10 +9267,10 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C250" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D250" t="n">
         <v>96</v>
@@ -9285,7 +9285,7 @@
         <v>12</v>
       </c>
       <c r="H250" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I250" t="s">
         <v>37</v>
@@ -9296,10 +9296,10 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C251" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D251" t="n">
         <v>96</v>
@@ -9314,7 +9314,7 @@
         <v>12</v>
       </c>
       <c r="H251" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I251" t="s">
         <v>37</v>
@@ -9325,10 +9325,10 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C252" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D252" t="n">
         <v>3</v>
@@ -9343,7 +9343,7 @@
         <v>12</v>
       </c>
       <c r="H252" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I252" t="s">
         <v>14</v>
@@ -9354,10 +9354,10 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C253" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D253" t="n">
         <v>3</v>
@@ -9372,7 +9372,7 @@
         <v>12</v>
       </c>
       <c r="H253" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I253" t="s">
         <v>14</v>
@@ -9383,10 +9383,10 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C254" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D254" t="n">
         <v>3</v>
@@ -9401,7 +9401,7 @@
         <v>12</v>
       </c>
       <c r="H254" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I254" t="s">
         <v>14</v>
@@ -9412,10 +9412,10 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C255" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D255" t="n">
         <v>3</v>
@@ -9430,7 +9430,7 @@
         <v>12</v>
       </c>
       <c r="H255" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I255" t="s">
         <v>14</v>
@@ -9441,10 +9441,10 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C256" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D256" t="n">
         <v>8</v>
@@ -9470,10 +9470,10 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C257" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D257" t="n">
         <v>97</v>
@@ -9499,10 +9499,10 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
+        <v>381</v>
+      </c>
+      <c r="C258" t="s">
         <v>380</v>
-      </c>
-      <c r="C258" t="s">
-        <v>379</v>
       </c>
       <c r="D258" t="n">
         <v>97</v>
@@ -9528,10 +9528,10 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C259" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D259" t="n">
         <v>97</v>
@@ -9557,10 +9557,10 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C260" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D260" t="n">
         <v>97</v>
@@ -9586,10 +9586,10 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C261" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D261" t="n">
         <v>97</v>
@@ -9615,10 +9615,10 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C262" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D262" t="n">
         <v>97</v>
@@ -9644,10 +9644,10 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C263" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D263" t="n">
         <v>97</v>
@@ -9662,7 +9662,7 @@
         <v>12</v>
       </c>
       <c r="H263" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I263" t="s">
         <v>14</v>
@@ -9673,10 +9673,10 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C264" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D264" t="n">
         <v>97</v>
@@ -9702,10 +9702,10 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C265" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D265" t="n">
         <v>8</v>
@@ -9731,10 +9731,10 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C266" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D266" t="n">
         <v>97</v>
@@ -9760,10 +9760,10 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C267" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D267" t="n">
         <v>97</v>
@@ -9789,10 +9789,10 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C268" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D268" t="n">
         <v>97</v>
@@ -9818,10 +9818,10 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C269" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D269" t="n">
         <v>8</v>
@@ -9836,7 +9836,7 @@
         <v>12</v>
       </c>
       <c r="H269" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I269" t="s">
         <v>59</v>
@@ -9847,10 +9847,10 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C270" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D270" t="n">
         <v>27</v>
@@ -9865,7 +9865,7 @@
         <v>12</v>
       </c>
       <c r="H270" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I270" t="s">
         <v>109</v>
@@ -9876,10 +9876,10 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C271" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D271" t="n">
         <v>27</v>
@@ -9894,7 +9894,7 @@
         <v>12</v>
       </c>
       <c r="H271" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I271" t="s">
         <v>109</v>
@@ -9905,10 +9905,10 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C272" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D272" t="n">
         <v>96</v>
@@ -9934,10 +9934,10 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C273" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D273" t="n">
         <v>96</v>
@@ -9963,10 +9963,10 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C274" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D274" t="n">
         <v>96</v>
@@ -9992,10 +9992,10 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C275" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D275" t="n">
         <v>96</v>
@@ -10010,7 +10010,7 @@
         <v>12</v>
       </c>
       <c r="H275" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I275" t="s">
         <v>59</v>
@@ -10021,10 +10021,10 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
+        <v>401</v>
+      </c>
+      <c r="C276" t="s">
         <v>400</v>
-      </c>
-      <c r="C276" t="s">
-        <v>399</v>
       </c>
       <c r="D276" t="n">
         <v>96</v>
@@ -10039,7 +10039,7 @@
         <v>12</v>
       </c>
       <c r="H276" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I276" t="s">
         <v>59</v>
@@ -10050,10 +10050,10 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C277" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D277" t="n">
         <v>96</v>
@@ -10068,7 +10068,7 @@
         <v>12</v>
       </c>
       <c r="H277" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I277" t="s">
         <v>59</v>
@@ -10079,10 +10079,10 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C278" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D278" t="n">
         <v>8</v>
@@ -10097,10 +10097,10 @@
         <v>43</v>
       </c>
       <c r="H278" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="I278" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="279">
@@ -10108,10 +10108,10 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C279" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D279" t="n">
         <v>8</v>
@@ -10126,10 +10126,10 @@
         <v>43</v>
       </c>
       <c r="H279" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="I279" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="280">
@@ -10137,16 +10137,16 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C280" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D280" t="n">
         <v>3</v>
       </c>
       <c r="E280" t="n">
-        <v>3180</v>
+        <v>3195</v>
       </c>
       <c r="F280" t="s">
         <v>156</v>
@@ -10158,7 +10158,7 @@
         <v>40</v>
       </c>
       <c r="I280" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
     </row>
     <row r="281">
@@ -10166,16 +10166,16 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
+        <v>411</v>
+      </c>
+      <c r="C281" t="s">
         <v>410</v>
-      </c>
-      <c r="C281" t="s">
-        <v>409</v>
       </c>
       <c r="D281" t="n">
         <v>1</v>
       </c>
       <c r="E281" t="n">
-        <v>1085</v>
+        <v>1090</v>
       </c>
       <c r="F281" t="s">
         <v>36</v>
@@ -10184,10 +10184,10 @@
         <v>27</v>
       </c>
       <c r="H281" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="I281" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
     </row>
     <row r="282">
@@ -10195,16 +10195,16 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C282" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D282" t="n">
         <v>1</v>
       </c>
       <c r="E282" t="n">
-        <v>1085</v>
+        <v>1090</v>
       </c>
       <c r="F282" t="s">
         <v>36</v>
@@ -10213,10 +10213,10 @@
         <v>27</v>
       </c>
       <c r="H282" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="I282" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
     </row>
     <row r="283">
@@ -10224,10 +10224,10 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C283" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D283" t="n">
         <v>1</v>
@@ -10242,7 +10242,7 @@
         <v>27</v>
       </c>
       <c r="H283" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="I283" t="s">
         <v>86</v>
@@ -10253,10 +10253,10 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C284" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D284" t="n">
         <v>1</v>
@@ -10271,7 +10271,7 @@
         <v>27</v>
       </c>
       <c r="H284" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="I284" t="s">
         <v>86</v>
@@ -10282,10 +10282,10 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C285" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D285" t="n">
         <v>3</v>
@@ -10300,7 +10300,7 @@
         <v>12</v>
       </c>
       <c r="H285" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I285" t="s">
         <v>14</v>
@@ -10311,10 +10311,10 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C286" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D286" t="n">
         <v>3</v>
@@ -10329,7 +10329,7 @@
         <v>12</v>
       </c>
       <c r="H286" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I286" t="s">
         <v>14</v>
@@ -10340,10 +10340,10 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C287" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D287" t="n">
         <v>88</v>
@@ -10358,7 +10358,7 @@
         <v>43</v>
       </c>
       <c r="H287" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I287" t="s">
         <v>45</v>
@@ -10369,10 +10369,10 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
+        <v>421</v>
+      </c>
+      <c r="C288" t="s">
         <v>420</v>
-      </c>
-      <c r="C288" t="s">
-        <v>419</v>
       </c>
       <c r="D288" t="n">
         <v>88</v>
@@ -10387,7 +10387,7 @@
         <v>43</v>
       </c>
       <c r="H288" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I288" t="s">
         <v>45</v>
@@ -10398,10 +10398,10 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C289" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D289" t="n">
         <v>7</v>
@@ -10416,7 +10416,7 @@
         <v>43</v>
       </c>
       <c r="H289" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I289" t="s">
         <v>45</v>
@@ -10427,10 +10427,10 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C290" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D290" t="n">
         <v>7</v>
@@ -10445,7 +10445,7 @@
         <v>43</v>
       </c>
       <c r="H290" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I290" t="s">
         <v>45</v>
@@ -10456,10 +10456,10 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C291" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D291" t="n">
         <v>97</v>
@@ -10485,10 +10485,10 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
+        <v>426</v>
+      </c>
+      <c r="C292" t="s">
         <v>425</v>
-      </c>
-      <c r="C292" t="s">
-        <v>424</v>
       </c>
       <c r="D292" t="n">
         <v>97</v>
@@ -10514,10 +10514,10 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C293" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D293" t="n">
         <v>97</v>
@@ -10543,10 +10543,10 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C294" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D294" t="n">
         <v>97</v>
@@ -10572,10 +10572,10 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C295" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D295" t="n">
         <v>97</v>
@@ -10601,10 +10601,10 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C296" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D296" t="n">
         <v>97</v>
@@ -10630,10 +10630,10 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C297" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D297" t="n">
         <v>97</v>
@@ -10659,10 +10659,10 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C298" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D298" t="n">
         <v>97</v>
@@ -10688,10 +10688,10 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C299" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D299" t="n">
         <v>97</v>
@@ -10717,10 +10717,10 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C300" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D300" t="n">
         <v>97</v>
@@ -10746,10 +10746,10 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C301" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D301" t="n">
         <v>97</v>
@@ -10775,10 +10775,10 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C302" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D302" t="n">
         <v>97</v>
@@ -10804,10 +10804,10 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C303" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D303" t="n">
         <v>97</v>
@@ -10833,10 +10833,10 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C304" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D304" t="n">
         <v>97</v>
@@ -10862,10 +10862,10 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C305" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D305" t="n">
         <v>97</v>
@@ -10891,10 +10891,10 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C306" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D306" t="n">
         <v>97</v>
@@ -10920,10 +10920,10 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C307" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D307" t="n">
         <v>97</v>
@@ -10949,10 +10949,10 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C308" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D308" t="n">
         <v>97</v>
@@ -10978,10 +10978,10 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C309" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D309" t="n">
         <v>97</v>
@@ -11007,10 +11007,10 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C310" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D310" t="n">
         <v>97</v>
@@ -11036,10 +11036,10 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C311" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D311" t="n">
         <v>97</v>
@@ -11065,10 +11065,10 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C312" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D312" t="n">
         <v>97</v>
@@ -11094,10 +11094,10 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C313" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D313" t="n">
         <v>89</v>
@@ -11112,7 +11112,7 @@
         <v>12</v>
       </c>
       <c r="H313" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I313" t="s">
         <v>14</v>
@@ -11123,10 +11123,10 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
+        <v>449</v>
+      </c>
+      <c r="C314" t="s">
         <v>448</v>
-      </c>
-      <c r="C314" t="s">
-        <v>447</v>
       </c>
       <c r="D314" t="n">
         <v>89</v>
@@ -11141,7 +11141,7 @@
         <v>12</v>
       </c>
       <c r="H314" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I314" t="s">
         <v>14</v>
@@ -11152,10 +11152,10 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C315" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D315" t="n">
         <v>89</v>
@@ -11170,7 +11170,7 @@
         <v>12</v>
       </c>
       <c r="H315" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I315" t="s">
         <v>14</v>
@@ -11181,10 +11181,10 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C316" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D316" t="n">
         <v>7</v>
@@ -11199,7 +11199,7 @@
         <v>12</v>
       </c>
       <c r="H316" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I316" t="s">
         <v>14</v>
@@ -11210,10 +11210,10 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C317" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D317" t="n">
         <v>7</v>
@@ -11228,7 +11228,7 @@
         <v>12</v>
       </c>
       <c r="H317" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I317" t="s">
         <v>14</v>
@@ -11239,10 +11239,10 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C318" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D318" t="n">
         <v>7</v>
@@ -11257,7 +11257,7 @@
         <v>12</v>
       </c>
       <c r="H318" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="I318" t="s">
         <v>14</v>
@@ -11268,16 +11268,16 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C319" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D319" t="n">
         <v>1</v>
       </c>
       <c r="E319" t="n">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="F319" t="s">
         <v>36</v>
@@ -11286,10 +11286,10 @@
         <v>27</v>
       </c>
       <c r="H319" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="I319" t="s">
-        <v>455</v>
+        <v>29</v>
       </c>
     </row>
     <row r="320">
@@ -11300,13 +11300,13 @@
         <v>456</v>
       </c>
       <c r="C320" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D320" t="n">
         <v>1</v>
       </c>
       <c r="E320" t="n">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="F320" t="s">
         <v>36</v>
@@ -11315,10 +11315,10 @@
         <v>27</v>
       </c>
       <c r="H320" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="I320" t="s">
-        <v>455</v>
+        <v>29</v>
       </c>
     </row>
     <row r="321">
@@ -11329,13 +11329,13 @@
         <v>457</v>
       </c>
       <c r="C321" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D321" t="n">
         <v>1</v>
       </c>
       <c r="E321" t="n">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="F321" t="s">
         <v>36</v>
@@ -11344,10 +11344,10 @@
         <v>27</v>
       </c>
       <c r="H321" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="I321" t="s">
-        <v>455</v>
+        <v>29</v>
       </c>
     </row>
     <row r="322">
@@ -11358,13 +11358,13 @@
         <v>458</v>
       </c>
       <c r="C322" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D322" t="n">
         <v>1</v>
       </c>
       <c r="E322" t="n">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="F322" t="s">
         <v>36</v>
@@ -11373,10 +11373,10 @@
         <v>27</v>
       </c>
       <c r="H322" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="I322" t="s">
-        <v>455</v>
+        <v>29</v>
       </c>
     </row>
     <row r="323">
@@ -11387,7 +11387,7 @@
         <v>459</v>
       </c>
       <c r="C323" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D323" t="n">
         <v>1</v>
@@ -11416,13 +11416,13 @@
         <v>460</v>
       </c>
       <c r="C324" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D324" t="n">
-        <v>95</v>
+        <v>167</v>
       </c>
       <c r="E324" t="n">
-        <v>16625</v>
+        <v>15865</v>
       </c>
       <c r="F324" t="s">
         <v>11</v>
@@ -11445,13 +11445,13 @@
         <v>462</v>
       </c>
       <c r="C325" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D325" t="n">
-        <v>95</v>
+        <v>167</v>
       </c>
       <c r="E325" t="n">
-        <v>16625</v>
+        <v>15865</v>
       </c>
       <c r="F325" t="s">
         <v>11</v>
@@ -11474,7 +11474,7 @@
         <v>463</v>
       </c>
       <c r="C326" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D326" t="n">
         <v>95</v>
@@ -11489,7 +11489,7 @@
         <v>12</v>
       </c>
       <c r="H326" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="I326" t="s">
         <v>60</v>
@@ -11500,10 +11500,10 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C327" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D327" t="n">
         <v>95</v>
@@ -11518,7 +11518,7 @@
         <v>12</v>
       </c>
       <c r="H327" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="I327" t="s">
         <v>60</v>
@@ -11529,10 +11529,10 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C328" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D328" t="n">
         <v>1</v>
@@ -11547,7 +11547,7 @@
         <v>27</v>
       </c>
       <c r="H328" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="I328" t="s">
         <v>29</v>
@@ -11558,10 +11558,10 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C329" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D329" t="n">
         <v>1</v>
@@ -11576,7 +11576,7 @@
         <v>27</v>
       </c>
       <c r="H329" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="I329" t="s">
         <v>29</v>
@@ -11587,10 +11587,10 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C330" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D330" t="n">
         <v>96</v>
@@ -11605,7 +11605,7 @@
         <v>12</v>
       </c>
       <c r="H330" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I330" t="s">
         <v>59</v>
@@ -11616,10 +11616,10 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C331" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D331" t="n">
         <v>96</v>
@@ -11634,7 +11634,7 @@
         <v>12</v>
       </c>
       <c r="H331" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I331" t="s">
         <v>59</v>
@@ -11645,10 +11645,10 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C332" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D332" t="n">
         <v>1</v>
@@ -11674,10 +11674,10 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C333" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D333" t="n">
         <v>3</v>
@@ -11692,7 +11692,7 @@
         <v>12</v>
       </c>
       <c r="H333" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="I333" t="s">
         <v>60</v>
@@ -11703,10 +11703,10 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C334" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D334" t="n">
         <v>3</v>
@@ -11721,7 +11721,7 @@
         <v>12</v>
       </c>
       <c r="H334" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="I334" t="s">
         <v>60</v>
@@ -11732,10 +11732,10 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C335" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D335" t="n">
         <v>3</v>
@@ -11750,7 +11750,7 @@
         <v>12</v>
       </c>
       <c r="H335" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="I335" t="s">
         <v>60</v>
@@ -11761,10 +11761,10 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C336" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D336" t="n">
         <v>3</v>
@@ -11779,7 +11779,7 @@
         <v>12</v>
       </c>
       <c r="H336" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="I336" t="s">
         <v>60</v>
@@ -11790,10 +11790,10 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C337" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D337" t="n">
         <v>19</v>
@@ -11819,10 +11819,10 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
+        <v>481</v>
+      </c>
+      <c r="C338" t="s">
         <v>480</v>
-      </c>
-      <c r="C338" t="s">
-        <v>479</v>
       </c>
       <c r="D338" t="n">
         <v>19</v>
@@ -11848,10 +11848,10 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C339" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D339" t="n">
         <v>5</v>
@@ -11877,10 +11877,10 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C340" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D340" t="n">
         <v>8</v>
@@ -11906,10 +11906,10 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
+        <v>485</v>
+      </c>
+      <c r="C341" t="s">
         <v>484</v>
-      </c>
-      <c r="C341" t="s">
-        <v>483</v>
       </c>
       <c r="D341" t="n">
         <v>5</v>
@@ -11927,7 +11927,7 @@
         <v>125</v>
       </c>
       <c r="I341" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="342">
@@ -11935,10 +11935,10 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C342" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D342" t="n">
         <v>8</v>
@@ -11964,10 +11964,10 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C343" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D343" t="n">
         <v>20</v>
@@ -11982,10 +11982,10 @@
         <v>43</v>
       </c>
       <c r="H343" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="I343" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="344">
@@ -11993,10 +11993,10 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C344" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D344" t="n">
         <v>20</v>
@@ -12011,10 +12011,10 @@
         <v>43</v>
       </c>
       <c r="H344" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="I344" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="345">
@@ -12022,10 +12022,10 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C345" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D345" t="n">
         <v>20</v>
@@ -12040,10 +12040,10 @@
         <v>43</v>
       </c>
       <c r="H345" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="I345" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="346">
@@ -12051,10 +12051,10 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C346" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D346" t="n">
         <v>63</v>
@@ -12069,7 +12069,7 @@
         <v>27</v>
       </c>
       <c r="H346" t="s">
-        <v>494</v>
+        <v>461</v>
       </c>
       <c r="I346" t="s">
         <v>29</v>
@@ -12083,7 +12083,7 @@
         <v>495</v>
       </c>
       <c r="C347" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D347" t="n">
         <v>63</v>
@@ -12112,7 +12112,7 @@
         <v>496</v>
       </c>
       <c r="C348" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D348" t="n">
         <v>63</v>
@@ -12156,7 +12156,7 @@
         <v>12</v>
       </c>
       <c r="H349" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="I349" t="s">
         <v>14</v>
@@ -12185,7 +12185,7 @@
         <v>12</v>
       </c>
       <c r="H350" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="I350" t="s">
         <v>14</v>
@@ -12214,7 +12214,7 @@
         <v>12</v>
       </c>
       <c r="H351" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="I351" t="s">
         <v>14</v>
@@ -12234,7 +12234,7 @@
         <v>1</v>
       </c>
       <c r="E352" t="n">
-        <v>1525</v>
+        <v>1530</v>
       </c>
       <c r="F352" t="s">
         <v>36</v>
@@ -12246,7 +12246,7 @@
         <v>184</v>
       </c>
       <c r="I352" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
     </row>
     <row r="353">
@@ -12263,7 +12263,7 @@
         <v>1</v>
       </c>
       <c r="E353" t="n">
-        <v>1525</v>
+        <v>1530</v>
       </c>
       <c r="F353" t="s">
         <v>36</v>
@@ -12275,7 +12275,7 @@
         <v>184</v>
       </c>
       <c r="I353" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
     </row>
     <row r="354">
@@ -12304,7 +12304,7 @@
         <v>505</v>
       </c>
       <c r="I354" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="355">
@@ -12333,7 +12333,7 @@
         <v>507</v>
       </c>
       <c r="I355" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="356">
@@ -12417,7 +12417,7 @@
         <v>12</v>
       </c>
       <c r="H358" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I358" t="s">
         <v>14</v>
@@ -12446,7 +12446,7 @@
         <v>12</v>
       </c>
       <c r="H359" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I359" t="s">
         <v>60</v>
@@ -12475,7 +12475,7 @@
         <v>12</v>
       </c>
       <c r="H360" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I360" t="s">
         <v>60</v>
@@ -12504,7 +12504,7 @@
         <v>12</v>
       </c>
       <c r="H361" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="I361" t="s">
         <v>60</v>
@@ -12611,7 +12611,7 @@
         <v>1</v>
       </c>
       <c r="E365" t="n">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="F365" t="s">
         <v>36</v>
@@ -12623,7 +12623,7 @@
         <v>519</v>
       </c>
       <c r="I365" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
     </row>
     <row r="366">
@@ -12640,7 +12640,7 @@
         <v>1</v>
       </c>
       <c r="E366" t="n">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="F366" t="s">
         <v>36</v>
@@ -12652,7 +12652,7 @@
         <v>519</v>
       </c>
       <c r="I366" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
     </row>
     <row r="367">
@@ -12669,7 +12669,7 @@
         <v>1</v>
       </c>
       <c r="E367" t="n">
-        <v>1095</v>
+        <v>1100</v>
       </c>
       <c r="F367" t="s">
         <v>36</v>
@@ -12681,7 +12681,7 @@
         <v>522</v>
       </c>
       <c r="I367" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
     </row>
     <row r="368">
@@ -12959,7 +12959,7 @@
         <v>15</v>
       </c>
       <c r="E377" t="n">
-        <v>27450</v>
+        <v>27525</v>
       </c>
       <c r="F377" t="s">
         <v>20</v>
@@ -12971,7 +12971,7 @@
         <v>539</v>
       </c>
       <c r="I377" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
     </row>
     <row r="378">
@@ -13046,7 +13046,7 @@
         <v>96</v>
       </c>
       <c r="E380" t="n">
-        <v>7200</v>
+        <v>7680</v>
       </c>
       <c r="F380" t="s">
         <v>11</v>
@@ -13055,10 +13055,10 @@
         <v>12</v>
       </c>
       <c r="H380" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I380" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
     </row>
     <row r="381">
@@ -13075,7 +13075,7 @@
         <v>96</v>
       </c>
       <c r="E381" t="n">
-        <v>4320</v>
+        <v>4608</v>
       </c>
       <c r="F381" t="s">
         <v>11</v>
@@ -13084,10 +13084,10 @@
         <v>12</v>
       </c>
       <c r="H381" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I381" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
     </row>
     <row r="382">
@@ -13104,7 +13104,7 @@
         <v>96</v>
       </c>
       <c r="E382" t="n">
-        <v>7200</v>
+        <v>7680</v>
       </c>
       <c r="F382" t="s">
         <v>11</v>
@@ -13113,10 +13113,10 @@
         <v>12</v>
       </c>
       <c r="H382" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I382" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
     </row>
     <row r="383">
@@ -13133,7 +13133,7 @@
         <v>96</v>
       </c>
       <c r="E383" t="n">
-        <v>4320</v>
+        <v>4608</v>
       </c>
       <c r="F383" t="s">
         <v>11</v>
@@ -13142,10 +13142,10 @@
         <v>12</v>
       </c>
       <c r="H383" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I383" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
     </row>
     <row r="384">
@@ -13548,7 +13548,7 @@
         <v>27</v>
       </c>
       <c r="H397" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="I397" t="s">
         <v>29</v>
@@ -13577,7 +13577,7 @@
         <v>27</v>
       </c>
       <c r="H398" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="I398" t="s">
         <v>29</v>
@@ -13606,7 +13606,7 @@
         <v>27</v>
       </c>
       <c r="H399" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="I399" t="s">
         <v>29</v>
@@ -13664,7 +13664,7 @@
         <v>27</v>
       </c>
       <c r="H401" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="I401" t="s">
         <v>29</v>
